--- a/数据表/Datas/BattleActionConfig_战斗行动配置.xlsx
+++ b/数据表/Datas/BattleActionConfig_战斗行动配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16040"/>
+    <workbookView windowHeight="16080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>行动</t>
     </r>
     <r>
@@ -101,6 +107,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>MP</t>
     </r>
     <r>
@@ -130,6 +142,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>技能</t>
     </r>
     <r>
@@ -150,6 +168,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>技能</t>
     </r>
     <r>
@@ -170,6 +194,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>技能</t>
     </r>
     <r>
@@ -190,6 +220,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>技能</t>
     </r>
     <r>
@@ -430,7 +466,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,18 +518,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -831,7 +855,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -897,95 +921,98 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1010,8 +1037,8 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1020,7 +1047,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1498,87 +1525,87 @@
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.9852941176471" style="1" customWidth="1"/>
-    <col min="4" max="5" width="19" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="36" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="12.9852941176471" style="3" customWidth="1"/>
+    <col min="4" max="5" width="19" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10" style="3" customWidth="1"/>
+    <col min="7" max="7" width="36" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:7">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:7">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -1590,7 +1617,7 @@
       <c r="E4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="12" t="s">
         <v>20</v>
       </c>
       <c r="G4" s="11" t="s">
@@ -1598,149 +1625,149 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:7">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="14">
         <v>0</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:7">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14">
         <v>101</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="14">
         <v>10</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:7">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14">
         <v>102</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="14">
         <v>10</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:7">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14">
         <v>103</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="14">
         <v>10</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:7">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14">
         <v>104</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="14">
         <v>10</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:7">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14">
         <v>201</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="14">
         <v>0</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:7">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14">
         <v>202</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="14">
         <v>8</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="14" t="s">
         <v>39</v>
       </c>
     </row>

--- a/数据表/Datas/BattleActionConfig_战斗行动配置.xlsx
+++ b/数据表/Datas/BattleActionConfig_战斗行动配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -47,7 +47,7 @@
     <t>mpCost</t>
   </si>
   <si>
-    <t>effects</t>
+    <t>*effects</t>
   </si>
   <si>
     <t>##type</t>
@@ -65,13 +65,31 @@
     <t>BattleTargetType</t>
   </si>
   <si>
-    <t>(list#sep=|),BattleEffect#sep=,</t>
+    <t>list,BattleEffect</t>
   </si>
   <si>
     <t>##group</t>
   </si>
   <si>
     <t>c</t>
+  </si>
+  <si>
+    <t>targetStat</t>
+  </si>
+  <si>
+    <t>flatValue</t>
+  </si>
+  <si>
+    <t>sourceStat</t>
+  </si>
+  <si>
+    <t>sourceScalePermille</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>durationRounds</t>
   </si>
   <si>
     <t>##</t>
@@ -97,22 +115,40 @@
     </r>
   </si>
   <si>
-    <t>显示名</t>
-  </si>
-  <si>
-    <t>行动类型</t>
-  </si>
-  <si>
-    <t>目标选择方式</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
+      <t>显示名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行动类型</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>目标选择方式</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>MP</t>
     </r>
     <r>
@@ -126,10 +162,81 @@
     </r>
   </si>
   <si>
-    <t>简单数值效果列表</t>
-  </si>
-  <si>
-    <t>普通攻击</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>目标属性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>目标值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>用于缩放的来源属性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>来源属性千分比，负数表示减少目标值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>附加状态</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>状态持续轮数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>普通攻击</t>
+    </r>
   </si>
   <si>
     <t>Attack</t>
@@ -138,7 +245,13 @@
     <t>SingleEnemy</t>
   </si>
   <si>
-    <t>HP,0,ATK,-1000,None,0</t>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>ATK</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <r>
@@ -164,9 +277,6 @@
     <t>Skill</t>
   </si>
   <si>
-    <t>HP,-5,ATK,-1500,None,0</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -190,7 +300,7 @@
     <t>SingleAlly</t>
   </si>
   <si>
-    <t>HP,20,MAT,1000,None,0</t>
+    <t>MAT</t>
   </si>
   <si>
     <r>
@@ -216,9 +326,6 @@
     <t>AllEnemies</t>
   </si>
   <si>
-    <t>HP,-2,MAT,-800,None,0</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -239,16 +346,29 @@
     </r>
   </si>
   <si>
-    <t>None,0,None,0,Stun,1</t>
-  </si>
-  <si>
-    <t>敌人攻击</t>
-  </si>
-  <si>
-    <t>敌人魔法</t>
-  </si>
-  <si>
-    <t>HP,-4,MAT,-1200,None,0</t>
+    <t>Stun</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人攻击</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人魔法</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -298,20 +418,8 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
     <font>
@@ -465,6 +573,18 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -672,7 +792,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -697,8 +817,82 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF9BBB9B"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BBB9B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BBB9B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BBB9B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BBB9B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9BBB9B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9BBB9B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BBB9B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF9EBDD7"/>
       </left>
+      <right style="thin">
+        <color rgb="FF9EBDD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9EBDD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EBDD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9EBDD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9EBDD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EBDD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9EBDD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EBDD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF9EBDD7"/>
       </right>
@@ -858,19 +1052,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -879,174 +1082,174 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1520,258 +1723,494 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.9852941176471" style="3" customWidth="1"/>
-    <col min="4" max="5" width="19" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10" style="3" customWidth="1"/>
-    <col min="7" max="7" width="36" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="3" max="3" width="12.9852941176471" style="2" customWidth="1"/>
+    <col min="4" max="5" width="19" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.2279411764706" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1102941176471" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.0735294117647" style="2" customWidth="1"/>
+    <col min="10" max="10" width="33.5735294117647" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.6617647058824" style="2" customWidth="1"/>
+    <col min="12" max="12" width="20.5808823529412" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+    <row r="1" customHeight="1" spans="1:12">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="7"/>
     </row>
-    <row r="2" customHeight="1" spans="1:7">
-      <c r="A2" s="6" t="s">
+    <row r="2" customHeight="1" spans="1:12">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="10" t="s">
         <v>12</v>
       </c>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="12"/>
     </row>
-    <row r="3" customHeight="1" spans="1:7">
-      <c r="A3" s="8" t="s">
+    <row r="3" customHeight="1" spans="1:12">
+      <c r="A3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="14" t="s">
         <v>14</v>
       </c>
+      <c r="H3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" customHeight="1" spans="1:7">
-      <c r="A4" s="10" t="s">
+    <row r="4" customHeight="1" spans="1:12">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="I4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="J4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="K4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="L4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="11" t="s">
+    </row>
+    <row r="5" customHeight="1" spans="1:12">
+      <c r="A5" s="15" t="s">
         <v>21</v>
       </c>
+      <c r="B5" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="5" customHeight="1" spans="1:7">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14">
+    <row r="6" customHeight="1" spans="1:12">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18">
         <v>1</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="C6" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="18">
         <v>0</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>25</v>
+      <c r="G6" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="2">
+        <v>-1000</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:7">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14">
+    <row r="7" customHeight="1" spans="1:12">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:12">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18">
         <v>101</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="14">
+      <c r="C8" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="18">
         <v>10</v>
       </c>
-      <c r="G6" s="14" t="s">
-        <v>28</v>
+      <c r="G8" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="2">
+        <v>-5</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:7">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14">
+    <row r="9" customHeight="1" spans="1:12">
+      <c r="A9" s="17"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:12">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18">
         <v>102</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="14">
+      <c r="C10" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="18">
         <v>10</v>
       </c>
-      <c r="G7" s="14" t="s">
-        <v>31</v>
+      <c r="G10" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="2">
+        <v>20</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:7">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14">
+    <row r="11" customHeight="1" spans="1:12">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:12">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18">
         <v>103</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="14">
+      <c r="C12" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="18">
         <v>10</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G12" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="2">
+        <v>-2</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="2">
+        <v>-800</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:12">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:12">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18">
+        <v>104</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="18">
+        <v>10</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:12">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:12">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18">
+        <v>201</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>34</v>
       </c>
+      <c r="E16" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="18">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="2">
+        <v>-1000</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" customHeight="1" spans="1:7">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14">
-        <v>104</v>
-      </c>
-      <c r="C9" s="15" t="s">
+    <row r="17" customHeight="1" spans="1:12">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:12">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18">
+        <v>202</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="14">
-        <v>10</v>
-      </c>
-      <c r="G9" s="14" t="s">
+      <c r="F18" s="18">
+        <v>8</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:7">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14">
-        <v>201</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="14">
+      <c r="H18" s="2">
+        <v>-4</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="2">
+        <v>-1200</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="2">
         <v>0</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:7">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14">
-        <v>202</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="14">
-        <v>8</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="G2:L2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/数据表/Datas/BattleActionConfig_战斗行动配置.xlsx
+++ b/数据表/Datas/BattleActionConfig_战斗行动配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -239,19 +239,41 @@
     </r>
   </si>
   <si>
-    <t>Attack</t>
+    <t>攻击</t>
   </si>
   <si>
     <t>SingleEnemy</t>
   </si>
   <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>ATK</t>
-  </si>
-  <si>
-    <t>None</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前生命</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无</t>
+    </r>
   </si>
   <si>
     <r>
@@ -274,7 +296,7 @@
     </r>
   </si>
   <si>
-    <t>Skill</t>
+    <t>技能</t>
   </si>
   <si>
     <r>
@@ -300,7 +322,15 @@
     <t>SingleAlly</t>
   </si>
   <si>
-    <t>MAT</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔力</t>
+    </r>
   </si>
   <si>
     <r>
@@ -346,7 +376,25 @@
     </r>
   </si>
   <si>
-    <t>Stun</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>眩晕</t>
+    </r>
   </si>
   <si>
     <r>
@@ -381,7 +429,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -420,6 +468,12 @@
       <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
     <font>
@@ -575,13 +629,12 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
+      <color rgb="FF9C0006"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
@@ -1052,153 +1105,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1250,6 +1303,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1908,7 +1964,7 @@
       <c r="C6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>34</v>
       </c>
       <c r="E6" s="18" t="s">
@@ -1953,7 +2009,7 @@
       <c r="C8" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E8" s="18" t="s">
@@ -1998,14 +2054,14 @@
       <c r="C10" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="18">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G10" s="18" t="s">
         <v>36</v>
@@ -2013,7 +2069,7 @@
       <c r="H10" s="2">
         <v>20</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="18" t="s">
         <v>43</v>
       </c>
       <c r="J10" s="2">
@@ -2043,7 +2099,7 @@
       <c r="C12" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E12" s="18" t="s">
@@ -2058,7 +2114,7 @@
       <c r="H12" s="2">
         <v>-2</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="18" t="s">
         <v>43</v>
       </c>
       <c r="J12" s="2">
@@ -2088,7 +2144,7 @@
       <c r="C14" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E14" s="18" t="s">
@@ -2098,7 +2154,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H14" s="2">
         <v>0</v>
@@ -2110,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L14" s="2">
         <v>1</v>
@@ -2131,9 +2187,9 @@
         <v>201</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="18" t="s">
@@ -2176,9 +2232,9 @@
         <v>202</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="18" t="s">
@@ -2193,7 +2249,7 @@
       <c r="H18" s="2">
         <v>-4</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="18" t="s">
         <v>43</v>
       </c>
       <c r="J18" s="2">

--- a/数据表/Datas/BattleActionConfig_战斗行动配置.xlsx
+++ b/数据表/Datas/BattleActionConfig_战斗行动配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -239,10 +239,26 @@
     </r>
   </si>
   <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>SingleEnemy</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单个敌方</t>
+    </r>
   </si>
   <si>
     <r>
@@ -296,7 +312,26 @@
     </r>
   </si>
   <si>
-    <t>技能</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技能</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>速度</t>
+    </r>
   </si>
   <si>
     <r>
@@ -319,7 +354,15 @@
     </r>
   </si>
   <si>
-    <t>SingleAlly</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单个友方</t>
+    </r>
   </si>
   <si>
     <r>
@@ -353,7 +396,15 @@
     </r>
   </si>
   <si>
-    <t>AllEnemies</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全体敌方</t>
+    </r>
   </si>
   <si>
     <r>
@@ -471,12 +522,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -629,12 +674,18 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF202020"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
@@ -1105,153 +1156,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1303,9 +1354,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1964,7 +2012,7 @@
       <c r="C6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>34</v>
       </c>
       <c r="E6" s="18" t="s">
@@ -2009,7 +2057,7 @@
       <c r="C8" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>40</v>
       </c>
       <c r="E8" s="18" t="s">
@@ -2019,16 +2067,16 @@
         <v>10</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H8" s="2">
         <v>-5</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" s="2">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>38</v>
@@ -2052,13 +2100,13 @@
         <v>102</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>40</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" s="18">
         <v>40</v>
@@ -2070,7 +2118,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J10" s="2">
         <v>1000</v>
@@ -2097,13 +2145,13 @@
         <v>103</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>40</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12" s="18">
         <v>10</v>
@@ -2115,7 +2163,7 @@
         <v>-2</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J12" s="2">
         <v>-800</v>
@@ -2142,9 +2190,9 @@
         <v>104</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>40</v>
       </c>
       <c r="E14" s="18" t="s">
@@ -2154,7 +2202,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H14" s="2">
         <v>0</v>
@@ -2166,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L14" s="2">
         <v>1</v>
@@ -2187,9 +2235,9 @@
         <v>201</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="18" t="s">
@@ -2232,9 +2280,9 @@
         <v>202</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="18" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="18" t="s">
@@ -2250,7 +2298,7 @@
         <v>-4</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J18" s="2">
         <v>-1200</v>
